--- a/exp/jack/Data/UK_Data/Num_GB_Buildings.xlsx
+++ b/exp/jack/Data/UK_Data/Num_GB_Buildings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JackLynch/CUBES/exp/jack/Data/UK_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8C9B44-96E8-4D48-8641-549DA9A54BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BE4F89-0ED5-E74B-A2C5-C3B4A4C06184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14060" activeTab="2" xr2:uid="{688A4600-F5B2-CE49-BAEC-B19C1EF7E076}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Modifcation" sheetId="2" r:id="rId2"/>
     <sheet name="Ambience" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="67">
   <si>
     <t>country_code</t>
   </si>
@@ -313,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -323,6 +323,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E778EE-603F-9745-88FA-1124B7276F85}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -1283,6 +1286,62 @@
         <v>25</v>
       </c>
     </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D25" s="6">
+        <v>1.6001650126667426</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D26" s="6">
+        <v>0.54460096439864059</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D27" s="6">
+        <v>0.53861233369007455</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D28" s="6">
+        <v>0.35006737879612665</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D29" s="6">
+        <v>0.3242301163755778</v>
+      </c>
+      <c r="E29" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D30" s="6">
+        <v>0.70913690976167632</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D31" s="6">
+        <v>0.40666581467367091</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1290,14 +1349,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4A1A6B-C215-5844-A8BE-C1C6C5C7FA63}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -1329,7 +1388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1353,10 +1412,10 @@
       </c>
       <c r="J2" s="3">
         <f>I2*F3</f>
-        <v>5.1692064908434228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3.1158947368421059</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1373,7 +1432,7 @@
         <v>1944</v>
       </c>
       <c r="F3">
-        <v>7.4916036099180044E-2</v>
+        <v>4.5157894736842112E-2</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1386,10 +1445,16 @@
       </c>
       <c r="J3" s="3">
         <f>(F2*G3)+(H3*F3)+(I3*F4)</f>
-        <v>1.9478169385786812</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1.174105263157895</v>
+      </c>
+      <c r="O3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>4.5157894736842112E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1406,7 +1471,7 @@
         <v>1969</v>
       </c>
       <c r="F4">
-        <v>0.20169794376602809</v>
+        <v>0.12479999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1419,10 +1484,16 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4:J8" si="0">(F3*G4)+(H4*F4)+(I4*F5)</f>
-        <v>4.033958875320562</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2.496</v>
+      </c>
+      <c r="O4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4">
+        <v>0.12479999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1439,7 +1510,7 @@
         <v>1979</v>
       </c>
       <c r="F5">
-        <v>0.1910040669815751</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1452,10 +1523,16 @@
       </c>
       <c r="J5" s="3">
         <f t="shared" si="0"/>
-        <v>3.05680481261092</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2.09</v>
+      </c>
+      <c r="O5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1472,7 +1549,7 @@
         <v>1989</v>
       </c>
       <c r="F6">
-        <v>0.13827442396502829</v>
+        <v>0.106</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1485,10 +1562,16 @@
       </c>
       <c r="J6" s="3">
         <f t="shared" si="0"/>
-        <v>1.3812706508832924</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1.0589999999999999</v>
+      </c>
+      <c r="O6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1505,7 +1588,7 @@
         <v>1999</v>
       </c>
       <c r="F7">
-        <v>0.1368008351980379</v>
+        <v>0.105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1518,10 +1601,16 @@
       </c>
       <c r="J7" s="3">
         <f t="shared" si="0"/>
-        <v>2.8262163931596538</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1.9529999999999998</v>
+      </c>
+      <c r="O7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1538,7 +1627,7 @@
         <v>2009</v>
       </c>
       <c r="F8">
-        <v>0.39875221909432818</v>
+        <v>0.252</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1551,10 +1640,16 @@
       </c>
       <c r="J8" s="3">
         <f t="shared" si="0"/>
-        <v>2.3925133145659689</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1.512</v>
+      </c>
+      <c r="O8" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1571,7 +1666,7 @@
         <v>2022</v>
       </c>
       <c r="F9">
-        <v>0.2375949225903834</v>
+        <v>0.1553846153846154</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1584,10 +1679,16 @@
       </c>
       <c r="J9" s="3">
         <f>(F8*G9)+(H9*F9)</f>
-        <v>3.088733993674984</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2.02</v>
+      </c>
+      <c r="O9" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>0.1553846153846154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1611,10 +1712,16 @@
       </c>
       <c r="J10" s="3">
         <f>I10*F11</f>
-        <v>1.162225114463213</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.50842105263157888</v>
+      </c>
+      <c r="O10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10">
+        <v>7.3684210526315788E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1631,7 +1738,7 @@
         <v>1944</v>
       </c>
       <c r="F11">
-        <v>1.6843842238597289E-2</v>
+        <v>7.3684210526315788E-3</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1644,10 +1751,16 @@
       </c>
       <c r="J11" s="3">
         <f>(F10*G11)+(H11*F11)+(I11*F12)</f>
-        <v>0.43793989820352952</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.19157894736842104</v>
+      </c>
+      <c r="O11" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1664,7 +1777,7 @@
         <v>1969</v>
       </c>
       <c r="F12">
-        <v>2.178403857594562E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1677,10 +1790,16 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" ref="J12:J16" si="1">(F11*G12)+(H12*F12)+(I12*F13)</f>
-        <v>0.43568077151891238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1697,7 +1816,7 @@
         <v>1979</v>
       </c>
       <c r="F13">
-        <v>5.3861233369007458E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1710,10 +1829,16 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
-        <v>0.68253926444941526</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="O13" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1730,7 +1855,7 @@
         <v>1989</v>
       </c>
       <c r="F14">
-        <v>3.5006737879612657E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1743,10 +1868,16 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="1"/>
-        <v>0.34748365255407171</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7.9000000000000015E-2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14">
+        <v>7.000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1763,7 +1894,7 @@
         <v>1999</v>
       </c>
       <c r="F15">
-        <v>3.2423011637557779E-2</v>
+        <v>7.000000000000001E-3</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1776,10 +1907,16 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="1"/>
-        <v>0.57546186864269055</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.183</v>
+      </c>
+      <c r="O15" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1796,7 +1933,7 @@
         <v>2009</v>
       </c>
       <c r="F16">
-        <v>7.0913690976167634E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1809,10 +1946,16 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="1"/>
-        <v>0.42548214585700583</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0.18</v>
+      </c>
+      <c r="O16" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16">
+        <v>1.5384615384615391E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1829,7 +1972,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>3.1281985744128528E-2</v>
+        <v>1.5384615384615391E-2</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1842,10 +1985,16 @@
       </c>
       <c r="J17" s="3">
         <f>(F16*G17)+(H17*F17)</f>
-        <v>0.40666581467367086</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="O17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17">
+        <v>1.4736842105263161E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1869,7 +2018,7 @@
       </c>
       <c r="J18" s="3">
         <f>I18*F19</f>
-        <v>0.43335115345383413</v>
+        <v>0.10168421052631581</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1879,10 +2028,16 @@
       </c>
       <c r="M18" s="3">
         <f>SUM(J18:J20)</f>
-        <v>0.92002057149247551</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="O18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1899,7 +2054,7 @@
         <v>1944</v>
       </c>
       <c r="F19">
-        <v>6.2804514993309293E-3</v>
+        <v>1.4736842105263161E-3</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1912,14 +2067,20 @@
       </c>
       <c r="J19" s="3">
         <f>(F18*G19)+(H19*F19)+(I19*F20)</f>
-        <v>0.16329173898260416</v>
+        <v>3.831578947368422E-2</v>
       </c>
       <c r="K19">
         <v>2</v>
       </c>
       <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1936,7 +2097,7 @@
         <v>1969</v>
       </c>
       <c r="F20">
-        <v>1.616888395280186E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1949,14 +2110,20 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" ref="J20:J24" si="2">(F19*G20)+(H20*F20)+(I20*F21)</f>
-        <v>0.3233776790560372</v>
+        <v>0.08</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1973,7 +2140,7 @@
         <v>1979</v>
       </c>
       <c r="F21">
-        <v>1.8079248666403449E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -1986,7 +2153,7 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>0.27769504460034705</v>
+        <v>6.3E-2</v>
       </c>
       <c r="K21">
         <v>4</v>
@@ -1996,10 +2163,16 @@
       </c>
       <c r="M21" s="3">
         <f>SUM(J21:J22)</f>
-        <v>0.43329286620094021</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="O21" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2016,7 +2189,7 @@
         <v>1989</v>
       </c>
       <c r="F22">
-        <v>1.6058138172303209E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2029,14 +2202,20 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>0.15559782160059316</v>
+        <v>2.8999999999999998E-2</v>
       </c>
       <c r="K22">
         <v>5</v>
       </c>
       <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2053,7 +2232,7 @@
         <v>1999</v>
       </c>
       <c r="F23">
-        <v>1.1074578049864279E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2066,7 +2245,7 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>0.23943237743806578</v>
+        <v>0.05</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -2076,10 +2255,16 @@
       </c>
       <c r="M23" s="3">
         <f>SUM(J23:J25)</f>
-        <v>0.66525461015101861</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23">
+        <v>3.8461538461538459E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2096,7 +2281,7 @@
         <v>2009</v>
       </c>
       <c r="F24">
-        <v>3.494029374732182E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2109,14 +2294,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>0.2096417624839309</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="K24">
         <v>7</v>
       </c>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2133,7 +2318,7 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>1.6629266940693999E-2</v>
+        <v>3.8461538461538459E-3</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2146,7 +2331,7 @@
       </c>
       <c r="J25" s="3">
         <f>(F24*G25)+(H25*F25)</f>
-        <v>0.21618047022902198</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2181,24 +2366,24 @@
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.9</v>
+      <c r="B2">
+        <v>0.22000000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.4</v>
+      <c r="B3">
+        <v>9.1999999999999998E-2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.7</v>
+      <c r="B4">
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2206,7 +2391,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="2">
-        <v>1.162225114463213</v>
+        <v>0.50842105263157888</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2214,7 +2399,7 @@
         <v>42</v>
       </c>
       <c r="B6" s="2">
-        <v>0.43793989820352952</v>
+        <v>0.19157894736842104</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -2222,7 +2407,7 @@
         <v>43</v>
       </c>
       <c r="B7" s="2">
-        <v>0.43568077151891238</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2230,7 +2415,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="2">
-        <v>0.68253926444941526</v>
+        <v>0.20800000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2238,7 +2423,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="2">
-        <v>0.34748365255407171</v>
+        <v>7.9000000000000015E-2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -2246,7 +2431,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="2">
-        <v>0.57546186864269055</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2254,7 +2439,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="2">
-        <v>0.42548214585700583</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -2262,7 +2447,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="2">
-        <v>0.40666581467367086</v>
+        <v>0.20000000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2270,7 +2455,7 @@
         <v>49</v>
       </c>
       <c r="B13" s="2">
-        <v>2.5846032454217114</v>
+        <v>1.557947368421053</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -2278,7 +2463,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="2">
-        <v>0.97390846928934061</v>
+        <v>0.58705263157894749</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -2286,7 +2471,7 @@
         <v>51</v>
       </c>
       <c r="B15" s="2">
-        <v>2.016979437660281</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -2294,7 +2479,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="2">
-        <v>1.52840240630546</v>
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -2302,7 +2487,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="2">
-        <v>0.69063532544164619</v>
+        <v>0.52949999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -2310,7 +2495,7 @@
         <v>54</v>
       </c>
       <c r="B18" s="2">
-        <v>1.4131081965798269</v>
+        <v>0.97649999999999992</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -2318,7 +2503,7 @@
         <v>55</v>
       </c>
       <c r="B19" s="2">
-        <v>1.1962566572829845</v>
+        <v>0.75600000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2326,7 +2511,7 @@
         <v>56</v>
       </c>
       <c r="B20" s="2">
-        <v>1.544366996837492</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -2334,7 +2519,7 @@
         <v>57</v>
       </c>
       <c r="B21" s="2">
-        <v>2.5846032454217114</v>
+        <v>1.557947368421053</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -2342,7 +2527,7 @@
         <v>58</v>
       </c>
       <c r="B22" s="2">
-        <v>0.97390846928934061</v>
+        <v>0.58705263157894749</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -2350,7 +2535,7 @@
         <v>59</v>
       </c>
       <c r="B23" s="2">
-        <v>2.016979437660281</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -2358,7 +2543,7 @@
         <v>60</v>
       </c>
       <c r="B24" s="2">
-        <v>1.52840240630546</v>
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -2366,7 +2551,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="2">
-        <v>0.69063532544164619</v>
+        <v>0.52949999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -2374,7 +2559,7 @@
         <v>62</v>
       </c>
       <c r="B26" s="2">
-        <v>1.4131081965798269</v>
+        <v>0.97649999999999992</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -2382,7 +2567,7 @@
         <v>63</v>
       </c>
       <c r="B27" s="2">
-        <v>1.1962566572829845</v>
+        <v>0.75600000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -2390,7 +2575,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="2">
-        <v>1.544366996837492</v>
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
